--- a/consent_forms/007_financial_authorization_form--consent_forms.xlsx
+++ b/consent_forms/007_financial_authorization_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transaction Type</t>
+          <t>What is the type of transaction?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Transaction Amount</t>
+          <t>What is the transaction amount?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>What is the financial institution involved?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>User Consent</t>
+          <t>Do you consent to this transaction?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date of transaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time of transaction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Second Financial Institution</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>User Consent</t>
+          <t>Second User Consent</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Second Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Second Time</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Additional Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Second Email Address</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Second Phone Number</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,172 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Second User Input</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>transaction_type_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Transaction Type</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>transaction_amount_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Transaction Amount</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>financial_institution_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Financial Institution</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_consent_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>User Consent</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>note_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1123,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_consent_2_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,114 +1157,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>transaction_type_2_choices</t>
+          <t>user_consent_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>transaction_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>financial_institution_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>financial_institution_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>user_consent_3_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>user_consent_3_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 2</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
